--- a/data/seat/05-mayo2026.xlsx
+++ b/data/seat/05-mayo2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe.sharepoint.com/sites/GOFEFEVALPARASO/Documentos compartidos/UNIDAD DE GESTION/Datos Operacionales/Energía/SEAT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe-my.sharepoint.com/personal/mvara_efevalparaiso_cl/Documents/Datos/Energía/SEAT/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{639001AF-ECAF-46FB-B4C0-4A99A373B3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD165CD2-9DC6-412D-96FD-B4D6D4C4EB85}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{639001AF-ECAF-46FB-B4C0-4A99A373B3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDE5DAF2-4903-4F95-BF6D-F7EBE108FE22}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEAT-SERs" sheetId="1" r:id="rId1"/>
@@ -2107,60 +2107,6 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2191,6 +2137,39 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2203,10 +2182,31 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3562,40 +3562,40 @@
                 <c:formatCode>#,##0\ "Kwh"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>24847</c:v>
+                  <c:v>24720</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29599</c:v>
+                  <c:v>29472</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>23628</c:v>
+                  <c:v>23501</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51107</c:v>
+                  <c:v>50980</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>54376</c:v>
+                  <c:v>54249</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>53592.270000000004</c:v>
+                  <c:v>53465.270000000004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>51589.29</c:v>
+                  <c:v>51462.29</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>51200</c:v>
+                  <c:v>51073</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>28900</c:v>
+                  <c:v>28773</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>21726</c:v>
+                  <c:v>21599</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>50669</c:v>
+                  <c:v>50542</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>50871</c:v>
+                  <c:v>50744</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3852,40 +3852,40 @@
                 <c:formatCode>#,##0\ "Kwh"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>6965</c:v>
+                  <c:v>7092</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7017</c:v>
+                  <c:v>7144</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6944</c:v>
+                  <c:v>7071</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7169</c:v>
+                  <c:v>7296</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7246</c:v>
+                  <c:v>7373</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7271.73</c:v>
+                  <c:v>7398.73</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7146.71</c:v>
+                  <c:v>7273.71</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7144</c:v>
+                  <c:v>7271</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6926</c:v>
+                  <c:v>7053</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6910</c:v>
+                  <c:v>7037</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7397</c:v>
+                  <c:v>7524</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7249</c:v>
+                  <c:v>7376</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7145,293 +7145,293 @@
       <c r="A1" s="126">
         <v>1.1111111E+55</v>
       </c>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="182" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="127"/>
-      <c r="D1" s="202" t="s">
+      <c r="D1" s="184" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="203"/>
-      <c r="M1" s="203"/>
-      <c r="N1" s="203"/>
-      <c r="O1" s="204"/>
-      <c r="P1" s="205"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="185"/>
+      <c r="K1" s="185"/>
+      <c r="L1" s="185"/>
+      <c r="M1" s="185"/>
+      <c r="N1" s="185"/>
+      <c r="O1" s="186"/>
+      <c r="P1" s="187"/>
       <c r="Q1" s="128"/>
-      <c r="R1" s="182" t="s">
+      <c r="R1" s="192" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="183"/>
-      <c r="T1" s="183"/>
-      <c r="U1" s="183"/>
-      <c r="V1" s="183"/>
-      <c r="W1" s="183"/>
-      <c r="X1" s="183"/>
-      <c r="Y1" s="183"/>
-      <c r="Z1" s="183"/>
-      <c r="AA1" s="184"/>
+      <c r="S1" s="193"/>
+      <c r="T1" s="193"/>
+      <c r="U1" s="193"/>
+      <c r="V1" s="193"/>
+      <c r="W1" s="193"/>
+      <c r="X1" s="193"/>
+      <c r="Y1" s="193"/>
+      <c r="Z1" s="193"/>
+      <c r="AA1" s="194"/>
       <c r="AB1" s="129"/>
-      <c r="AC1" s="182" t="s">
+      <c r="AC1" s="192" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="183"/>
-      <c r="AE1" s="183"/>
-      <c r="AF1" s="183"/>
-      <c r="AG1" s="183"/>
-      <c r="AH1" s="183"/>
-      <c r="AI1" s="183"/>
-      <c r="AJ1" s="183"/>
-      <c r="AK1" s="184"/>
+      <c r="AD1" s="193"/>
+      <c r="AE1" s="193"/>
+      <c r="AF1" s="193"/>
+      <c r="AG1" s="193"/>
+      <c r="AH1" s="193"/>
+      <c r="AI1" s="193"/>
+      <c r="AJ1" s="193"/>
+      <c r="AK1" s="194"/>
       <c r="AL1" s="130"/>
-      <c r="AM1" s="182" t="s">
+      <c r="AM1" s="192" t="s">
         <v>4</v>
       </c>
-      <c r="AN1" s="183"/>
-      <c r="AO1" s="183"/>
-      <c r="AP1" s="183"/>
-      <c r="AQ1" s="183"/>
-      <c r="AR1" s="183"/>
-      <c r="AS1" s="183"/>
-      <c r="AT1" s="183"/>
-      <c r="AU1" s="184"/>
+      <c r="AN1" s="193"/>
+      <c r="AO1" s="193"/>
+      <c r="AP1" s="193"/>
+      <c r="AQ1" s="193"/>
+      <c r="AR1" s="193"/>
+      <c r="AS1" s="193"/>
+      <c r="AT1" s="193"/>
+      <c r="AU1" s="194"/>
       <c r="AV1" s="130"/>
-      <c r="AW1" s="182" t="s">
+      <c r="AW1" s="192" t="s">
         <v>57</v>
       </c>
-      <c r="AX1" s="183"/>
-      <c r="AY1" s="183"/>
-      <c r="AZ1" s="183"/>
-      <c r="BA1" s="183"/>
-      <c r="BB1" s="183"/>
-      <c r="BC1" s="183"/>
-      <c r="BD1" s="183"/>
-      <c r="BE1" s="183"/>
-      <c r="BF1" s="183"/>
-      <c r="BG1" s="183"/>
-      <c r="BH1" s="184"/>
+      <c r="AX1" s="193"/>
+      <c r="AY1" s="193"/>
+      <c r="AZ1" s="193"/>
+      <c r="BA1" s="193"/>
+      <c r="BB1" s="193"/>
+      <c r="BC1" s="193"/>
+      <c r="BD1" s="193"/>
+      <c r="BE1" s="193"/>
+      <c r="BF1" s="193"/>
+      <c r="BG1" s="193"/>
+      <c r="BH1" s="194"/>
       <c r="BI1" s="130"/>
-      <c r="BJ1" s="182" t="s">
+      <c r="BJ1" s="192" t="s">
         <v>5</v>
       </c>
-      <c r="BK1" s="183"/>
-      <c r="BL1" s="183"/>
-      <c r="BM1" s="183"/>
-      <c r="BN1" s="183"/>
-      <c r="BO1" s="183"/>
-      <c r="BP1" s="183"/>
-      <c r="BQ1" s="183"/>
-      <c r="BR1" s="184"/>
+      <c r="BK1" s="193"/>
+      <c r="BL1" s="193"/>
+      <c r="BM1" s="193"/>
+      <c r="BN1" s="193"/>
+      <c r="BO1" s="193"/>
+      <c r="BP1" s="193"/>
+      <c r="BQ1" s="193"/>
+      <c r="BR1" s="194"/>
       <c r="BS1" s="131"/>
     </row>
     <row r="2" spans="1:71" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="200"/>
+      <c r="B2" s="182"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="207"/>
-      <c r="G2" s="207"/>
-      <c r="H2" s="207"/>
-      <c r="I2" s="207"/>
-      <c r="J2" s="207"/>
-      <c r="K2" s="207"/>
-      <c r="L2" s="207"/>
-      <c r="M2" s="207"/>
-      <c r="N2" s="207"/>
-      <c r="O2" s="208"/>
-      <c r="P2" s="209"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="189"/>
+      <c r="F2" s="189"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="189"/>
+      <c r="J2" s="189"/>
+      <c r="K2" s="189"/>
+      <c r="L2" s="189"/>
+      <c r="M2" s="189"/>
+      <c r="N2" s="189"/>
+      <c r="O2" s="190"/>
+      <c r="P2" s="191"/>
       <c r="Q2" s="57"/>
-      <c r="R2" s="185"/>
-      <c r="S2" s="186"/>
-      <c r="T2" s="186"/>
-      <c r="U2" s="186"/>
-      <c r="V2" s="186"/>
-      <c r="W2" s="186"/>
-      <c r="X2" s="186"/>
-      <c r="Y2" s="186"/>
-      <c r="Z2" s="186"/>
-      <c r="AA2" s="187"/>
+      <c r="R2" s="195"/>
+      <c r="S2" s="196"/>
+      <c r="T2" s="196"/>
+      <c r="U2" s="196"/>
+      <c r="V2" s="196"/>
+      <c r="W2" s="196"/>
+      <c r="X2" s="196"/>
+      <c r="Y2" s="196"/>
+      <c r="Z2" s="196"/>
+      <c r="AA2" s="197"/>
       <c r="AB2" s="59"/>
-      <c r="AC2" s="185"/>
-      <c r="AD2" s="186"/>
-      <c r="AE2" s="186"/>
-      <c r="AF2" s="186"/>
-      <c r="AG2" s="186"/>
-      <c r="AH2" s="186"/>
-      <c r="AI2" s="186"/>
-      <c r="AJ2" s="186"/>
-      <c r="AK2" s="187"/>
+      <c r="AC2" s="195"/>
+      <c r="AD2" s="196"/>
+      <c r="AE2" s="196"/>
+      <c r="AF2" s="196"/>
+      <c r="AG2" s="196"/>
+      <c r="AH2" s="196"/>
+      <c r="AI2" s="196"/>
+      <c r="AJ2" s="196"/>
+      <c r="AK2" s="197"/>
       <c r="AL2" s="58"/>
-      <c r="AM2" s="185"/>
-      <c r="AN2" s="186"/>
-      <c r="AO2" s="186"/>
-      <c r="AP2" s="186"/>
-      <c r="AQ2" s="186"/>
-      <c r="AR2" s="186"/>
-      <c r="AS2" s="186"/>
-      <c r="AT2" s="186"/>
-      <c r="AU2" s="187"/>
+      <c r="AM2" s="195"/>
+      <c r="AN2" s="196"/>
+      <c r="AO2" s="196"/>
+      <c r="AP2" s="196"/>
+      <c r="AQ2" s="196"/>
+      <c r="AR2" s="196"/>
+      <c r="AS2" s="196"/>
+      <c r="AT2" s="196"/>
+      <c r="AU2" s="197"/>
       <c r="AV2" s="58"/>
-      <c r="AW2" s="185"/>
-      <c r="AX2" s="186"/>
-      <c r="AY2" s="186"/>
-      <c r="AZ2" s="186"/>
-      <c r="BA2" s="186"/>
-      <c r="BB2" s="186"/>
-      <c r="BC2" s="186"/>
-      <c r="BD2" s="186"/>
-      <c r="BE2" s="186"/>
-      <c r="BF2" s="186"/>
-      <c r="BG2" s="186"/>
-      <c r="BH2" s="187"/>
+      <c r="AW2" s="195"/>
+      <c r="AX2" s="196"/>
+      <c r="AY2" s="196"/>
+      <c r="AZ2" s="196"/>
+      <c r="BA2" s="196"/>
+      <c r="BB2" s="196"/>
+      <c r="BC2" s="196"/>
+      <c r="BD2" s="196"/>
+      <c r="BE2" s="196"/>
+      <c r="BF2" s="196"/>
+      <c r="BG2" s="196"/>
+      <c r="BH2" s="197"/>
       <c r="BI2" s="58"/>
-      <c r="BJ2" s="185"/>
-      <c r="BK2" s="186"/>
-      <c r="BL2" s="186"/>
-      <c r="BM2" s="186"/>
-      <c r="BN2" s="186"/>
-      <c r="BO2" s="186"/>
-      <c r="BP2" s="186"/>
-      <c r="BQ2" s="186"/>
-      <c r="BR2" s="187"/>
+      <c r="BJ2" s="195"/>
+      <c r="BK2" s="196"/>
+      <c r="BL2" s="196"/>
+      <c r="BM2" s="196"/>
+      <c r="BN2" s="196"/>
+      <c r="BO2" s="196"/>
+      <c r="BP2" s="196"/>
+      <c r="BQ2" s="196"/>
+      <c r="BR2" s="197"/>
       <c r="BS2" s="134"/>
     </row>
     <row r="3" spans="1:71" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="200"/>
+      <c r="B3" s="182"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="188" t="s">
+      <c r="D3" s="201" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="188" t="s">
+      <c r="E3" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="188" t="s">
+      <c r="F3" s="201" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="188" t="s">
+      <c r="G3" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="188" t="s">
+      <c r="H3" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="210" t="s">
+      <c r="I3" s="203" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="211"/>
-      <c r="K3" s="212"/>
-      <c r="L3" s="213"/>
-      <c r="M3" s="210" t="s">
+      <c r="J3" s="204"/>
+      <c r="K3" s="205"/>
+      <c r="L3" s="206"/>
+      <c r="M3" s="203" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="211"/>
-      <c r="O3" s="212"/>
-      <c r="P3" s="213"/>
+      <c r="N3" s="204"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="206"/>
       <c r="Q3" s="57"/>
-      <c r="R3" s="192" t="s">
+      <c r="R3" s="207" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="193"/>
-      <c r="T3" s="214"/>
-      <c r="U3" s="214"/>
-      <c r="V3" s="192" t="s">
+      <c r="S3" s="199"/>
+      <c r="T3" s="208"/>
+      <c r="U3" s="208"/>
+      <c r="V3" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="193"/>
-      <c r="X3" s="193"/>
-      <c r="Y3" s="193"/>
-      <c r="Z3" s="193"/>
-      <c r="AA3" s="194"/>
+      <c r="W3" s="199"/>
+      <c r="X3" s="199"/>
+      <c r="Y3" s="199"/>
+      <c r="Z3" s="199"/>
+      <c r="AA3" s="200"/>
       <c r="AB3" s="59"/>
-      <c r="AC3" s="190" t="s">
+      <c r="AC3" s="209" t="s">
         <v>15</v>
       </c>
-      <c r="AD3" s="215" t="s">
+      <c r="AD3" s="211" t="s">
         <v>9</v>
       </c>
-      <c r="AE3" s="192" t="s">
+      <c r="AE3" s="207" t="s">
         <v>13</v>
       </c>
-      <c r="AF3" s="193"/>
-      <c r="AG3" s="194"/>
-      <c r="AH3" s="192" t="s">
+      <c r="AF3" s="199"/>
+      <c r="AG3" s="200"/>
+      <c r="AH3" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="AI3" s="193"/>
-      <c r="AJ3" s="193"/>
-      <c r="AK3" s="194"/>
+      <c r="AI3" s="199"/>
+      <c r="AJ3" s="199"/>
+      <c r="AK3" s="200"/>
       <c r="AL3" s="58"/>
-      <c r="AM3" s="195" t="s">
+      <c r="AM3" s="212" t="s">
         <v>15</v>
       </c>
-      <c r="AN3" s="190" t="s">
+      <c r="AN3" s="209" t="s">
         <v>9</v>
       </c>
-      <c r="AO3" s="199" t="s">
+      <c r="AO3" s="198" t="s">
         <v>13</v>
       </c>
-      <c r="AP3" s="193"/>
-      <c r="AQ3" s="194"/>
-      <c r="AR3" s="192" t="s">
+      <c r="AP3" s="199"/>
+      <c r="AQ3" s="200"/>
+      <c r="AR3" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="AS3" s="193"/>
-      <c r="AT3" s="193"/>
-      <c r="AU3" s="194"/>
+      <c r="AS3" s="199"/>
+      <c r="AT3" s="199"/>
+      <c r="AU3" s="200"/>
       <c r="AV3" s="58"/>
-      <c r="AW3" s="190" t="s">
+      <c r="AW3" s="209" t="s">
         <v>15</v>
       </c>
-      <c r="AX3" s="190" t="s">
+      <c r="AX3" s="209" t="s">
         <v>9</v>
       </c>
-      <c r="AY3" s="199" t="s">
+      <c r="AY3" s="198" t="s">
         <v>13</v>
       </c>
-      <c r="AZ3" s="199"/>
-      <c r="BA3" s="193"/>
-      <c r="BB3" s="194"/>
-      <c r="BC3" s="192" t="s">
+      <c r="AZ3" s="198"/>
+      <c r="BA3" s="199"/>
+      <c r="BB3" s="200"/>
+      <c r="BC3" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="BD3" s="199"/>
-      <c r="BE3" s="199"/>
-      <c r="BF3" s="193"/>
-      <c r="BG3" s="193"/>
-      <c r="BH3" s="194"/>
+      <c r="BD3" s="198"/>
+      <c r="BE3" s="198"/>
+      <c r="BF3" s="199"/>
+      <c r="BG3" s="199"/>
+      <c r="BH3" s="200"/>
       <c r="BI3" s="58"/>
-      <c r="BJ3" s="195" t="s">
+      <c r="BJ3" s="212" t="s">
         <v>16</v>
       </c>
-      <c r="BK3" s="190" t="s">
+      <c r="BK3" s="209" t="s">
         <v>17</v>
       </c>
-      <c r="BL3" s="196" t="s">
+      <c r="BL3" s="213" t="s">
         <v>18</v>
       </c>
-      <c r="BM3" s="197"/>
-      <c r="BN3" s="198"/>
-      <c r="BO3" s="199" t="s">
+      <c r="BM3" s="214"/>
+      <c r="BN3" s="215"/>
+      <c r="BO3" s="198" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="193"/>
-      <c r="BQ3" s="193"/>
-      <c r="BR3" s="194"/>
+      <c r="BP3" s="199"/>
+      <c r="BQ3" s="199"/>
+      <c r="BR3" s="200"/>
       <c r="BS3" s="134"/>
     </row>
     <row r="4" spans="1:71" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="201"/>
+      <c r="B4" s="183"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="202"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="202"/>
+      <c r="H4" s="202"/>
       <c r="I4" s="79" t="s">
         <v>3</v>
       </c>
@@ -7488,8 +7488,8 @@
         <v>24</v>
       </c>
       <c r="AB4" s="59"/>
-      <c r="AC4" s="191"/>
-      <c r="AD4" s="183"/>
+      <c r="AC4" s="210"/>
+      <c r="AD4" s="193"/>
       <c r="AE4" s="61" t="s">
         <v>27</v>
       </c>
@@ -7512,8 +7512,8 @@
         <v>24</v>
       </c>
       <c r="AL4" s="60"/>
-      <c r="AM4" s="182"/>
-      <c r="AN4" s="191"/>
+      <c r="AM4" s="192"/>
+      <c r="AN4" s="210"/>
       <c r="AO4" s="122" t="s">
         <v>27</v>
       </c>
@@ -7536,8 +7536,8 @@
         <v>24</v>
       </c>
       <c r="AV4" s="60"/>
-      <c r="AW4" s="191"/>
-      <c r="AX4" s="191"/>
+      <c r="AW4" s="210"/>
+      <c r="AX4" s="210"/>
       <c r="AY4" s="122" t="s">
         <v>27</v>
       </c>
@@ -7569,8 +7569,8 @@
         <v>24</v>
       </c>
       <c r="BI4" s="60"/>
-      <c r="BJ4" s="182"/>
-      <c r="BK4" s="191"/>
+      <c r="BJ4" s="192"/>
+      <c r="BK4" s="210"/>
       <c r="BL4" s="122" t="s">
         <v>32</v>
       </c>
@@ -7918,19 +7918,19 @@
       </c>
       <c r="E7" s="158">
         <f t="shared" ref="E7:E10" si="23">F7/D7</f>
-        <v>0.78105746259273234</v>
+        <v>0.77706525839305918</v>
       </c>
       <c r="F7" s="86">
         <f t="shared" ref="F7:F37" si="24">D7-H7</f>
-        <v>24847</v>
+        <v>24720</v>
       </c>
       <c r="G7" s="158">
         <f t="shared" ref="G7:G10" si="25">H7/D7</f>
-        <v>0.21894253740726768</v>
+        <v>0.22293474160694077</v>
       </c>
       <c r="H7" s="145">
         <f t="shared" ref="H7:H37" si="26">U7+AG7+AQ7+BB7</f>
-        <v>6965</v>
+        <v>7092</v>
       </c>
       <c r="I7" s="159">
         <f t="shared" ref="I7:I10" si="27">AE7/(AE7+AO7+BL7+AY7)</f>
@@ -8072,11 +8072,11 @@
       </c>
       <c r="AW7" s="109">
         <f t="shared" ref="AW7:AW10" si="42">BA7/AZ7</f>
-        <v>0.29401598617411967</v>
+        <v>0.26658025491466841</v>
       </c>
       <c r="AX7" s="109">
         <f t="shared" ref="AX7:AX10" si="43">BB7/AZ7</f>
-        <v>0.70598401382588027</v>
+        <v>0.73341974508533159</v>
       </c>
       <c r="AY7" s="110">
         <f t="shared" ref="AY7" si="44">BA7+BB7</f>
@@ -8087,11 +8087,11 @@
       </c>
       <c r="BA7" s="119">
         <f t="shared" ref="BA7:BA39" si="45">AZ7-BB7</f>
-        <v>1361</v>
+        <v>1234</v>
       </c>
       <c r="BB7" s="112">
-        <f>2697+571</f>
-        <v>3268</v>
+        <f>2697+698</f>
+        <v>3395</v>
       </c>
       <c r="BC7" s="111">
         <v>2067</v>
@@ -8159,19 +8159,19 @@
       </c>
       <c r="E8" s="158">
         <f t="shared" si="23"/>
-        <v>0.80836246449639504</v>
+        <v>0.80489403539436311</v>
       </c>
       <c r="F8" s="86">
         <f t="shared" si="24"/>
-        <v>29599</v>
+        <v>29472</v>
       </c>
       <c r="G8" s="158">
         <f t="shared" si="25"/>
-        <v>0.19163753550360499</v>
+        <v>0.19510596460563687</v>
       </c>
       <c r="H8" s="145">
         <f t="shared" si="26"/>
-        <v>7017</v>
+        <v>7144</v>
       </c>
       <c r="I8" s="159">
         <f t="shared" si="27"/>
@@ -8313,11 +8313,11 @@
       </c>
       <c r="AW8" s="109">
         <f t="shared" si="42"/>
-        <v>0.33245861929753734</v>
+        <v>0.30682276947920872</v>
       </c>
       <c r="AX8" s="109">
         <f t="shared" si="43"/>
-        <v>0.66754138070246261</v>
+        <v>0.69317723052079128</v>
       </c>
       <c r="AY8" s="110">
         <f>BA8+BB8</f>
@@ -8328,11 +8328,11 @@
       </c>
       <c r="BA8" s="119">
         <f t="shared" si="45"/>
-        <v>1647</v>
+        <v>1520</v>
       </c>
       <c r="BB8" s="112">
-        <f>2736+571</f>
-        <v>3307</v>
+        <f>2736+698</f>
+        <v>3434</v>
       </c>
       <c r="BC8" s="111">
         <v>1477</v>
@@ -8402,19 +8402,19 @@
       </c>
       <c r="E9" s="158">
         <f t="shared" si="23"/>
-        <v>0.77286405861572682</v>
+        <v>0.76870993065550175</v>
       </c>
       <c r="F9" s="86">
         <f t="shared" si="24"/>
-        <v>23628</v>
+        <v>23501</v>
       </c>
       <c r="G9" s="158">
         <f t="shared" si="25"/>
-        <v>0.2271359413842732</v>
+        <v>0.23129006934449822</v>
       </c>
       <c r="H9" s="145">
         <f t="shared" si="26"/>
-        <v>6944</v>
+        <v>7071</v>
       </c>
       <c r="I9" s="159">
         <f t="shared" si="27"/>
@@ -8556,11 +8556,11 @@
       </c>
       <c r="AW9" s="109">
         <f t="shared" si="42"/>
-        <v>0.44</v>
+        <v>0.41829059829059828</v>
       </c>
       <c r="AX9" s="109">
         <f t="shared" si="43"/>
-        <v>0.56000000000000005</v>
+        <v>0.58170940170940166</v>
       </c>
       <c r="AY9" s="110">
         <f t="shared" ref="AY9:AY39" si="54">BA9+BB9</f>
@@ -8571,11 +8571,11 @@
       </c>
       <c r="BA9" s="119">
         <f t="shared" si="45"/>
-        <v>2574</v>
+        <v>2447</v>
       </c>
       <c r="BB9" s="112">
-        <f>2705+571</f>
-        <v>3276</v>
+        <f>2705+698</f>
+        <v>3403</v>
       </c>
       <c r="BC9" s="111">
         <v>3036</v>
@@ -8642,19 +8642,19 @@
       </c>
       <c r="E10" s="158">
         <f t="shared" si="23"/>
-        <v>0.8769819479717208</v>
+        <v>0.87480266318896283</v>
       </c>
       <c r="F10" s="86">
         <f t="shared" si="24"/>
-        <v>51107</v>
+        <v>50980</v>
       </c>
       <c r="G10" s="158">
         <f t="shared" si="25"/>
-        <v>0.12301805202827923</v>
+        <v>0.12519733681103715</v>
       </c>
       <c r="H10" s="145">
         <f t="shared" si="26"/>
-        <v>7169</v>
+        <v>7296</v>
       </c>
       <c r="I10" s="159">
         <f t="shared" si="27"/>
@@ -8796,11 +8796,11 @@
       </c>
       <c r="AW10" s="109">
         <f t="shared" si="42"/>
-        <v>0.6648351648351648</v>
+        <v>0.6521478521478522</v>
       </c>
       <c r="AX10" s="109">
         <f t="shared" si="43"/>
-        <v>0.33516483516483514</v>
+        <v>0.34785214785214785</v>
       </c>
       <c r="AY10" s="110">
         <f t="shared" si="54"/>
@@ -8811,11 +8811,11 @@
       </c>
       <c r="BA10" s="119">
         <f t="shared" si="45"/>
-        <v>6655</v>
+        <v>6528</v>
       </c>
       <c r="BB10" s="112">
-        <f>2784+571</f>
-        <v>3355</v>
+        <f>2784+698</f>
+        <v>3482</v>
       </c>
       <c r="BC10" s="111">
         <v>3863</v>
@@ -8885,19 +8885,19 @@
       </c>
       <c r="E11" s="158">
         <f t="shared" ref="E11:E24" si="55">F11/D11</f>
-        <v>0.88241212553958004</v>
+        <v>0.88035117328226931</v>
       </c>
       <c r="F11" s="86">
         <f t="shared" si="24"/>
-        <v>54376</v>
+        <v>54249</v>
       </c>
       <c r="G11" s="158">
         <f t="shared" ref="G11:G24" si="56">H11/D11</f>
-        <v>0.11758787446041997</v>
+        <v>0.11964882671773068</v>
       </c>
       <c r="H11" s="145">
         <f t="shared" si="26"/>
-        <v>7246</v>
+        <v>7373</v>
       </c>
       <c r="I11" s="159">
         <f t="shared" ref="I11:I24" si="57">AE11/(AE11+AO11+BL11+AY11)</f>
@@ -9039,11 +9039,11 @@
       </c>
       <c r="AW11" s="109">
         <f t="shared" ref="AW11:AW25" si="69">BA11/AZ11</f>
-        <v>0.71648314701185167</v>
+        <v>0.7058081869378835</v>
       </c>
       <c r="AX11" s="109">
         <f t="shared" ref="AX11:AX25" si="70">BB11/AZ11</f>
-        <v>0.28351685298814827</v>
+        <v>0.2941918130621165</v>
       </c>
       <c r="AY11" s="110">
         <f t="shared" si="54"/>
@@ -9054,11 +9054,11 @@
       </c>
       <c r="BA11" s="119">
         <f t="shared" si="45"/>
-        <v>8524</v>
+        <v>8397</v>
       </c>
       <c r="BB11" s="112">
-        <f>2802+571</f>
-        <v>3373</v>
+        <f>2802+698</f>
+        <v>3500</v>
       </c>
       <c r="BC11" s="111">
         <v>3798</v>
@@ -9125,19 +9125,19 @@
       </c>
       <c r="E12" s="158">
         <f t="shared" si="55"/>
-        <v>0.88052494085173505</v>
+        <v>0.8784383215036804</v>
       </c>
       <c r="F12" s="86">
         <f t="shared" si="24"/>
-        <v>53592.270000000004</v>
+        <v>53465.270000000004</v>
       </c>
       <c r="G12" s="158">
         <f>H12/D12</f>
-        <v>0.11947505914826498</v>
+        <v>0.12156167849631966</v>
       </c>
       <c r="H12" s="145">
         <f t="shared" si="26"/>
-        <v>7271.73</v>
+        <v>7398.73</v>
       </c>
       <c r="I12" s="159">
         <f t="shared" si="57"/>
@@ -9279,11 +9279,11 @@
       </c>
       <c r="AW12" s="109">
         <f t="shared" si="69"/>
-        <v>0.65568287877216636</v>
+        <v>0.64251270351550349</v>
       </c>
       <c r="AX12" s="109">
         <f t="shared" si="70"/>
-        <v>0.34431712122783364</v>
+        <v>0.35748729648449651</v>
       </c>
       <c r="AY12" s="110">
         <f t="shared" si="54"/>
@@ -9294,11 +9294,11 @@
       </c>
       <c r="BA12" s="119">
         <f t="shared" si="45"/>
-        <v>6322.75</v>
+        <v>6195.75</v>
       </c>
       <c r="BB12" s="112">
-        <f>2749.25+571</f>
-        <v>3320.25</v>
+        <f>2749.25+698</f>
+        <v>3447.25</v>
       </c>
       <c r="BC12" s="111">
         <v>3683.99</v>
@@ -9365,19 +9365,19 @@
       </c>
       <c r="E13" s="158">
         <f t="shared" si="55"/>
-        <v>0.87832487741759735</v>
+        <v>0.87616266003813681</v>
       </c>
       <c r="F13" s="86">
         <f t="shared" si="24"/>
-        <v>51589.29</v>
+        <v>51462.29</v>
       </c>
       <c r="G13" s="158">
         <f t="shared" si="56"/>
-        <v>0.12167512258240261</v>
+        <v>0.12383733996186325</v>
       </c>
       <c r="H13" s="145">
         <f t="shared" si="26"/>
-        <v>7146.71</v>
+        <v>7273.71</v>
       </c>
       <c r="I13" s="159">
         <f t="shared" si="57"/>
@@ -9519,11 +9519,11 @@
       </c>
       <c r="AW13" s="168">
         <f t="shared" si="69"/>
-        <v>0.62620332300760351</v>
+        <v>0.61189749366375668</v>
       </c>
       <c r="AX13" s="168">
         <f t="shared" si="70"/>
-        <v>0.37379667699239649</v>
+        <v>0.38810250633624332</v>
       </c>
       <c r="AY13" s="110">
         <f t="shared" si="54"/>
@@ -9534,11 +9534,11 @@
       </c>
       <c r="BA13" s="119">
         <f t="shared" si="45"/>
-        <v>5559.12</v>
+        <v>5432.12</v>
       </c>
       <c r="BB13" s="112">
-        <f>2747.38+571</f>
-        <v>3318.38</v>
+        <f>2747.38+698</f>
+        <v>3445.38</v>
       </c>
       <c r="BC13" s="111">
         <v>4140.63</v>
@@ -9605,19 +9605,19 @@
       </c>
       <c r="E14" s="158">
         <f t="shared" si="55"/>
-        <v>0.87755381873028937</v>
+        <v>0.87537707390648567</v>
       </c>
       <c r="F14" s="86">
         <f t="shared" si="24"/>
-        <v>51200</v>
+        <v>51073</v>
       </c>
       <c r="G14" s="158">
         <f t="shared" si="56"/>
-        <v>0.12244618126971069</v>
+        <v>0.12462292609351433</v>
       </c>
       <c r="H14" s="145">
         <f t="shared" si="26"/>
-        <v>7144</v>
+        <v>7271</v>
       </c>
       <c r="I14" s="159">
         <f t="shared" si="57"/>
@@ -9759,11 +9759,11 @@
       </c>
       <c r="AW14" s="109">
         <f t="shared" si="69"/>
-        <v>0.65546655570581502</v>
+        <v>0.64225527930926873</v>
       </c>
       <c r="AX14" s="109">
         <f t="shared" si="70"/>
-        <v>0.34453344429418498</v>
+        <v>0.35774472069073132</v>
       </c>
       <c r="AY14" s="110">
         <f t="shared" si="54"/>
@@ -9774,11 +9774,11 @@
       </c>
       <c r="BA14" s="119">
         <f t="shared" si="45"/>
-        <v>6301</v>
+        <v>6174</v>
       </c>
       <c r="BB14" s="112">
-        <f>2741+571</f>
-        <v>3312</v>
+        <f>2741+698</f>
+        <v>3439</v>
       </c>
       <c r="BC14" s="111">
         <v>3993</v>
@@ -9845,19 +9845,19 @@
       </c>
       <c r="E15" s="158">
         <f t="shared" si="55"/>
-        <v>0.80667671523474571</v>
+        <v>0.80313180371797022</v>
       </c>
       <c r="F15" s="86">
         <f t="shared" si="24"/>
-        <v>28900</v>
+        <v>28773</v>
       </c>
       <c r="G15" s="158">
         <f t="shared" si="56"/>
-        <v>0.19332328476525429</v>
+        <v>0.19686819628202981</v>
       </c>
       <c r="H15" s="145">
         <f t="shared" si="26"/>
-        <v>6926</v>
+        <v>7053</v>
       </c>
       <c r="I15" s="159">
         <f t="shared" si="57"/>
@@ -9999,11 +9999,11 @@
       </c>
       <c r="AW15" s="168">
         <f t="shared" si="69"/>
-        <v>0.84600154529650373</v>
+        <v>0.83986864979717979</v>
       </c>
       <c r="AX15" s="168">
         <f t="shared" si="70"/>
-        <v>0.15399845470349624</v>
+        <v>0.16013135020282016</v>
       </c>
       <c r="AY15" s="110">
         <f t="shared" si="54"/>
@@ -10014,11 +10014,11 @@
       </c>
       <c r="BA15" s="119">
         <f t="shared" si="45"/>
-        <v>17519</v>
+        <v>17392</v>
       </c>
       <c r="BB15" s="112">
-        <f>2618+571</f>
-        <v>3189</v>
+        <f>2618+698</f>
+        <v>3316</v>
       </c>
       <c r="BC15" s="111">
         <v>4636</v>
@@ -10085,19 +10085,19 @@
       </c>
       <c r="E16" s="158">
         <f t="shared" si="55"/>
-        <v>0.75869534851236209</v>
+        <v>0.75426037156027381</v>
       </c>
       <c r="F16" s="86">
         <f t="shared" si="24"/>
-        <v>21726</v>
+        <v>21599</v>
       </c>
       <c r="G16" s="158">
         <f t="shared" si="56"/>
-        <v>0.24130465148763794</v>
+        <v>0.24573962843972622</v>
       </c>
       <c r="H16" s="145">
         <f t="shared" si="26"/>
-        <v>6910</v>
+        <v>7037</v>
       </c>
       <c r="I16" s="159">
         <f t="shared" si="57"/>
@@ -10239,11 +10239,11 @@
       </c>
       <c r="AW16" s="109">
         <f t="shared" si="69"/>
-        <v>0.81191113179015939</v>
+        <v>0.80452483424450394</v>
       </c>
       <c r="AX16" s="109">
         <f t="shared" si="70"/>
-        <v>0.18808886820984064</v>
+        <v>0.19547516575549612</v>
       </c>
       <c r="AY16" s="110">
         <f t="shared" si="54"/>
@@ -10254,11 +10254,11 @@
       </c>
       <c r="BA16" s="119">
         <f t="shared" si="45"/>
-        <v>13960</v>
+        <v>13833</v>
       </c>
       <c r="BB16" s="112">
-        <f>2663+571</f>
-        <v>3234</v>
+        <f>2663+698</f>
+        <v>3361</v>
       </c>
       <c r="BC16" s="111">
         <v>4555</v>
@@ -10325,19 +10325,19 @@
       </c>
       <c r="E17" s="158">
         <f t="shared" si="55"/>
-        <v>0.87261047773223577</v>
+        <v>0.8704233114042641</v>
       </c>
       <c r="F17" s="86">
         <f t="shared" si="24"/>
-        <v>50669</v>
+        <v>50542</v>
       </c>
       <c r="G17" s="158">
         <f t="shared" si="56"/>
-        <v>0.12738952226776426</v>
+        <v>0.1295766885957359</v>
       </c>
       <c r="H17" s="145">
         <f t="shared" si="26"/>
-        <v>7397</v>
+        <v>7524</v>
       </c>
       <c r="I17" s="159">
         <f t="shared" si="57"/>
@@ -10479,11 +10479,11 @@
       </c>
       <c r="AW17" s="109">
         <f t="shared" si="69"/>
-        <v>0.65759084648797539</v>
+        <v>0.64413603135925412</v>
       </c>
       <c r="AX17" s="109">
         <f t="shared" si="70"/>
-        <v>0.34240915351202456</v>
+        <v>0.35586396864074582</v>
       </c>
       <c r="AY17" s="110">
         <f t="shared" si="54"/>
@@ -10494,11 +10494,11 @@
       </c>
       <c r="BA17" s="119">
         <f t="shared" si="45"/>
-        <v>6207</v>
+        <v>6080</v>
       </c>
       <c r="BB17" s="112">
-        <f>2661+571</f>
-        <v>3232</v>
+        <f>2661+698</f>
+        <v>3359</v>
       </c>
       <c r="BC17" s="111">
         <v>4486</v>
@@ -10565,19 +10565,19 @@
       </c>
       <c r="E18" s="158">
         <f t="shared" si="55"/>
-        <v>0.8752752924982794</v>
+        <v>0.87309015829318648</v>
       </c>
       <c r="F18" s="86">
         <f t="shared" si="24"/>
-        <v>50871</v>
+        <v>50744</v>
       </c>
       <c r="G18" s="158">
         <f t="shared" si="56"/>
-        <v>0.12472470750172057</v>
+        <v>0.12690984170681349</v>
       </c>
       <c r="H18" s="145">
         <f t="shared" si="26"/>
-        <v>7249</v>
+        <v>7376</v>
       </c>
       <c r="I18" s="159">
         <f t="shared" si="57"/>
@@ -10719,11 +10719,11 @@
       </c>
       <c r="AW18" s="109">
         <f t="shared" si="69"/>
-        <v>0.66608784473953009</v>
+        <v>0.65311542390194077</v>
       </c>
       <c r="AX18" s="109">
         <f t="shared" si="70"/>
-        <v>0.33391215526046986</v>
+        <v>0.34688457609805923</v>
       </c>
       <c r="AY18" s="110">
         <f t="shared" si="54"/>
@@ -10734,11 +10734,11 @@
       </c>
       <c r="BA18" s="119">
         <f t="shared" si="45"/>
-        <v>6521</v>
+        <v>6394</v>
       </c>
       <c r="BB18" s="112">
-        <f>2698+571</f>
-        <v>3269</v>
+        <f>2698+698</f>
+        <v>3396</v>
       </c>
       <c r="BC18" s="111">
         <v>4590</v>
@@ -10805,19 +10805,19 @@
       </c>
       <c r="E19" s="158">
         <f t="shared" si="55"/>
-        <v>0.87934732396225168</v>
+        <v>0.87725202930112844</v>
       </c>
       <c r="F19" s="86">
         <f t="shared" si="24"/>
-        <v>53299</v>
+        <v>53172</v>
       </c>
       <c r="G19" s="158">
         <f t="shared" si="56"/>
-        <v>0.1206526760377483</v>
+        <v>0.12274797069887151</v>
       </c>
       <c r="H19" s="145">
         <f t="shared" si="26"/>
-        <v>7313</v>
+        <v>7440</v>
       </c>
       <c r="I19" s="159">
         <f t="shared" si="57"/>
@@ -10959,11 +10959,11 @@
       </c>
       <c r="AW19" s="109">
         <f t="shared" ref="AW19" si="77">BA19/AZ19</f>
-        <v>0.66268719237616502</v>
+        <v>0.64938737040527805</v>
       </c>
       <c r="AX19" s="109">
         <f t="shared" ref="AX19" si="78">BB19/AZ19</f>
-        <v>0.33731280762383498</v>
+        <v>0.35061262959472195</v>
       </c>
       <c r="AY19" s="110">
         <f t="shared" si="54"/>
@@ -10974,11 +10974,11 @@
       </c>
       <c r="BA19" s="119">
         <f t="shared" si="45"/>
-        <v>6328</v>
+        <v>6201</v>
       </c>
       <c r="BB19" s="112">
-        <f>2650+571</f>
-        <v>3221</v>
+        <f>2650+698</f>
+        <v>3348</v>
       </c>
       <c r="BC19" s="180">
         <v>4234</v>
@@ -11045,19 +11045,19 @@
       </c>
       <c r="E20" s="158">
         <f t="shared" si="55"/>
-        <v>0.87969526333222925</v>
+        <v>0.87759191785359392</v>
       </c>
       <c r="F20" s="86">
         <f t="shared" si="24"/>
-        <v>53116</v>
+        <v>52989</v>
       </c>
       <c r="G20" s="158">
         <f t="shared" si="56"/>
-        <v>0.12030473666777078</v>
+        <v>0.1224080821464061</v>
       </c>
       <c r="H20" s="145">
         <f t="shared" si="26"/>
-        <v>7264</v>
+        <v>7391</v>
       </c>
       <c r="I20" s="159">
         <f t="shared" si="57"/>
@@ -11199,11 +11199,11 @@
       </c>
       <c r="AW20" s="109">
         <f t="shared" si="69"/>
-        <v>0.6680489321998756</v>
+        <v>0.65488285299606053</v>
       </c>
       <c r="AX20" s="109">
         <f t="shared" si="70"/>
-        <v>0.3319510678001244</v>
+        <v>0.34511714700393947</v>
       </c>
       <c r="AY20" s="110">
         <f t="shared" si="54"/>
@@ -11214,11 +11214,11 @@
       </c>
       <c r="BA20" s="119">
         <f t="shared" si="45"/>
-        <v>6444</v>
+        <v>6317</v>
       </c>
       <c r="BB20" s="112">
-        <f>2631+571</f>
-        <v>3202</v>
+        <f>2631+698</f>
+        <v>3329</v>
       </c>
       <c r="BC20" s="111">
         <v>4219</v>
@@ -11286,19 +11286,19 @@
       </c>
       <c r="E21" s="158">
         <f t="shared" si="55"/>
-        <v>0.88089820951627262</v>
+        <v>0.8788043657466944</v>
       </c>
       <c r="F21" s="86">
         <f t="shared" si="24"/>
-        <v>53430</v>
+        <v>53303</v>
       </c>
       <c r="G21" s="158">
         <f t="shared" si="56"/>
-        <v>0.11910179048372738</v>
+        <v>0.12119563425330564</v>
       </c>
       <c r="H21" s="145">
         <f t="shared" si="26"/>
-        <v>7224</v>
+        <v>7351</v>
       </c>
       <c r="I21" s="159">
         <f t="shared" si="57"/>
@@ -11440,11 +11440,11 @@
       </c>
       <c r="AW21" s="109">
         <f t="shared" si="69"/>
-        <v>0.67214602662363854</v>
+        <v>0.65933844292053245</v>
       </c>
       <c r="AX21" s="109">
         <f t="shared" si="70"/>
-        <v>0.32785397337636146</v>
+        <v>0.34066155707946755</v>
       </c>
       <c r="AY21" s="110">
         <f t="shared" si="54"/>
@@ -11455,11 +11455,11 @@
       </c>
       <c r="BA21" s="119">
         <f t="shared" si="45"/>
-        <v>6665</v>
+        <v>6538</v>
       </c>
       <c r="BB21" s="112">
-        <f>2680+571</f>
-        <v>3251</v>
+        <f>2680+698</f>
+        <v>3378</v>
       </c>
       <c r="BC21" s="111">
         <v>4118</v>
@@ -11527,19 +11527,19 @@
       </c>
       <c r="E22" s="158">
         <f t="shared" si="55"/>
-        <v>0.80433335350723234</v>
+        <v>0.80049022574592987</v>
       </c>
       <c r="F22" s="86">
         <f t="shared" si="24"/>
-        <v>26580</v>
+        <v>26453</v>
       </c>
       <c r="G22" s="158">
         <f t="shared" si="56"/>
-        <v>0.19566664649276766</v>
+        <v>0.19950977425407007</v>
       </c>
       <c r="H22" s="145">
         <f t="shared" si="26"/>
-        <v>6466</v>
+        <v>6593</v>
       </c>
       <c r="I22" s="159">
         <f t="shared" si="57"/>
@@ -11681,11 +11681,11 @@
       </c>
       <c r="AW22" s="109">
         <f t="shared" si="69"/>
-        <v>0.53198104826769321</v>
+        <v>0.51317737636955874</v>
       </c>
       <c r="AX22" s="109">
         <f t="shared" si="70"/>
-        <v>0.46801895173230679</v>
+        <v>0.48682262363044121</v>
       </c>
       <c r="AY22" s="110">
         <f t="shared" si="54"/>
@@ -11696,11 +11696,11 @@
       </c>
       <c r="BA22" s="119">
         <f t="shared" si="45"/>
-        <v>3593</v>
+        <v>3466</v>
       </c>
       <c r="BB22" s="112">
-        <f>2590+571</f>
-        <v>3161</v>
+        <f>2590+698</f>
+        <v>3288</v>
       </c>
       <c r="BC22" s="111">
         <v>2225</v>
@@ -11768,19 +11768,19 @@
       </c>
       <c r="E23" s="158">
         <f t="shared" si="55"/>
-        <v>0.74572726617148621</v>
+        <v>0.74114804932573741</v>
       </c>
       <c r="F23" s="86">
         <f t="shared" si="24"/>
-        <v>20682</v>
+        <v>20555</v>
       </c>
       <c r="G23" s="158">
         <f t="shared" si="56"/>
-        <v>0.25427273382851373</v>
+        <v>0.25885195067426264</v>
       </c>
       <c r="H23" s="145">
         <f t="shared" si="26"/>
-        <v>7052</v>
+        <v>7179</v>
       </c>
       <c r="I23" s="159">
         <f t="shared" si="57"/>
@@ -11923,11 +11923,11 @@
       </c>
       <c r="AW23" s="109">
         <f t="shared" si="69"/>
-        <v>0.40670371034235525</v>
+        <v>0.38393977415307401</v>
       </c>
       <c r="AX23" s="109">
         <f t="shared" si="70"/>
-        <v>0.59329628965764469</v>
+        <v>0.61606022584692599</v>
       </c>
       <c r="AY23" s="110">
         <f t="shared" si="54"/>
@@ -11938,11 +11938,11 @@
       </c>
       <c r="BA23" s="119">
         <f t="shared" si="45"/>
-        <v>2269</v>
+        <v>2142</v>
       </c>
       <c r="BB23" s="112">
-        <f>2739+571</f>
-        <v>3310</v>
+        <f>2739+698</f>
+        <v>3437</v>
       </c>
       <c r="BC23" s="111">
         <v>2132</v>
@@ -12010,19 +12010,19 @@
       </c>
       <c r="E24" s="158">
         <f t="shared" si="55"/>
-        <v>0.86742287784679095</v>
+        <v>0.86523171152518985</v>
       </c>
       <c r="F24" s="86">
         <f t="shared" si="24"/>
-        <v>50275.83</v>
+        <v>50148.83</v>
       </c>
       <c r="G24" s="158">
         <f t="shared" si="56"/>
-        <v>0.1325771221532091</v>
+        <v>0.13476828847481021</v>
       </c>
       <c r="H24" s="145">
         <f t="shared" si="26"/>
-        <v>7684.17</v>
+        <v>7811.17</v>
       </c>
       <c r="I24" s="159">
         <f t="shared" si="57"/>
@@ -12164,11 +12164,11 @@
       </c>
       <c r="AW24" s="109">
         <f t="shared" si="69"/>
-        <v>0.62589012804626187</v>
+        <v>0.61277571251548946</v>
       </c>
       <c r="AX24" s="109">
         <f t="shared" si="70"/>
-        <v>0.37410987195373813</v>
+        <v>0.38722428748451054</v>
       </c>
       <c r="AY24" s="110">
         <f t="shared" si="54"/>
@@ -12179,11 +12179,11 @@
       </c>
       <c r="BA24" s="119">
         <f t="shared" si="45"/>
-        <v>6061.12</v>
+        <v>5934.12</v>
       </c>
       <c r="BB24" s="112">
-        <f>3051.88+571</f>
-        <v>3622.88</v>
+        <f>3051.88+698</f>
+        <v>3749.88</v>
       </c>
       <c r="BC24" s="111">
         <v>4158</v>
@@ -12251,19 +12251,19 @@
       </c>
       <c r="E25" s="158">
         <f t="shared" ref="E25:E36" si="83">F25/D25</f>
-        <v>0.86918150296726016</v>
+        <v>0.86706441288257652</v>
       </c>
       <c r="F25" s="86">
         <f t="shared" si="24"/>
-        <v>52140.46</v>
+        <v>52013.46</v>
       </c>
       <c r="G25" s="158">
         <f t="shared" ref="G25:G36" si="84">H25/D25</f>
-        <v>0.13081849703273987</v>
+        <v>0.13293558711742348</v>
       </c>
       <c r="H25" s="145">
         <f t="shared" si="26"/>
-        <v>7847.54</v>
+        <v>7974.54</v>
       </c>
       <c r="I25" s="159">
         <f t="shared" ref="I25:I36" si="85">AE25/(AE25+AO25+BL25+AY25)</f>
@@ -12405,11 +12405,11 @@
       </c>
       <c r="AW25" s="168">
         <f t="shared" si="69"/>
-        <v>0.62106659674882014</v>
+        <v>0.60774724698479288</v>
       </c>
       <c r="AX25" s="168">
         <f t="shared" si="70"/>
-        <v>0.37893340325117986</v>
+        <v>0.39225275301520712</v>
       </c>
       <c r="AY25" s="110">
         <f t="shared" si="54"/>
@@ -12420,11 +12420,11 @@
       </c>
       <c r="BA25" s="119">
         <f t="shared" si="45"/>
-        <v>5921.87</v>
+        <v>5794.87</v>
       </c>
       <c r="BB25" s="112">
-        <f>3042.13+571</f>
-        <v>3613.13</v>
+        <f>3042.13+698</f>
+        <v>3740.13</v>
       </c>
       <c r="BC25" s="111">
         <v>4038.57</v>
@@ -12492,19 +12492,19 @@
       </c>
       <c r="E26" s="158">
         <f t="shared" si="83"/>
-        <v>0.87024638912489383</v>
+        <v>0.86808836023789293</v>
       </c>
       <c r="F26" s="86">
         <f t="shared" si="24"/>
-        <v>51214</v>
+        <v>51087</v>
       </c>
       <c r="G26" s="158">
         <f t="shared" si="84"/>
-        <v>0.1297536108751062</v>
+        <v>0.13191163976210704</v>
       </c>
       <c r="H26" s="145">
         <f t="shared" si="26"/>
-        <v>7636</v>
+        <v>7763</v>
       </c>
       <c r="I26" s="159">
         <f t="shared" si="85"/>
@@ -12646,11 +12646,11 @@
       </c>
       <c r="AW26" s="109">
         <f t="shared" ref="AW26:AW36" si="97">BA26/AZ26</f>
-        <v>0.61523605150214589</v>
+        <v>0.60160944206008582</v>
       </c>
       <c r="AX26" s="109">
         <f t="shared" ref="AX26:AX36" si="98">BB26/AZ26</f>
-        <v>0.38476394849785406</v>
+        <v>0.39839055793991418</v>
       </c>
       <c r="AY26" s="110">
         <f t="shared" si="54"/>
@@ -12661,11 +12661,11 @@
       </c>
       <c r="BA26" s="119">
         <f t="shared" si="45"/>
-        <v>5734</v>
+        <v>5607</v>
       </c>
       <c r="BB26" s="112">
-        <f>3015+571</f>
-        <v>3586</v>
+        <f>3015+698</f>
+        <v>3713</v>
       </c>
       <c r="BC26" s="111">
         <v>4100</v>
@@ -12733,19 +12733,19 @@
       </c>
       <c r="E27" s="158">
         <f t="shared" si="83"/>
-        <v>0.82549210206561363</v>
+        <v>0.82240583232077769</v>
       </c>
       <c r="F27" s="86">
         <f t="shared" si="24"/>
-        <v>33969</v>
+        <v>33842</v>
       </c>
       <c r="G27" s="158">
         <f t="shared" si="84"/>
-        <v>0.1745078979343864</v>
+        <v>0.17759416767922237</v>
       </c>
       <c r="H27" s="145">
         <f t="shared" si="26"/>
-        <v>7181</v>
+        <v>7308</v>
       </c>
       <c r="I27" s="159">
         <f t="shared" si="85"/>
@@ -12887,11 +12887,11 @@
       </c>
       <c r="AW27" s="109">
         <f t="shared" si="97"/>
-        <v>0.51640287769784177</v>
+        <v>0.49812949640287768</v>
       </c>
       <c r="AX27" s="109">
         <f t="shared" si="98"/>
-        <v>0.48359712230215829</v>
+        <v>0.50187050359712226</v>
       </c>
       <c r="AY27" s="110">
         <f t="shared" si="54"/>
@@ -12902,11 +12902,11 @@
       </c>
       <c r="BA27" s="119">
         <f t="shared" si="45"/>
-        <v>3589</v>
+        <v>3462</v>
       </c>
       <c r="BB27" s="112">
-        <f>2790+571</f>
-        <v>3361</v>
+        <f>2790+698</f>
+        <v>3488</v>
       </c>
       <c r="BC27" s="111">
         <v>3670</v>
@@ -12974,19 +12974,19 @@
       </c>
       <c r="E28" s="158">
         <f t="shared" si="83"/>
-        <v>0.87479634247714044</v>
+        <v>0.87268495428096426</v>
       </c>
       <c r="F28" s="86">
         <f t="shared" si="24"/>
-        <v>52619</v>
+        <v>52492</v>
       </c>
       <c r="G28" s="158">
         <f t="shared" si="84"/>
-        <v>0.12520365752285953</v>
+        <v>0.12731504571903574</v>
       </c>
       <c r="H28" s="145">
         <f t="shared" si="26"/>
-        <v>7531</v>
+        <v>7658</v>
       </c>
       <c r="I28" s="159">
         <f t="shared" si="85"/>
@@ -13128,11 +13128,11 @@
       </c>
       <c r="AW28" s="109">
         <f t="shared" si="97"/>
-        <v>0.62423280423280425</v>
+        <v>0.61079365079365078</v>
       </c>
       <c r="AX28" s="109">
         <f t="shared" si="98"/>
-        <v>0.37576719576719575</v>
+        <v>0.38920634920634922</v>
       </c>
       <c r="AY28" s="110">
         <f t="shared" si="54"/>
@@ -13143,11 +13143,11 @@
       </c>
       <c r="BA28" s="119">
         <f t="shared" si="45"/>
-        <v>5899</v>
+        <v>5772</v>
       </c>
       <c r="BB28" s="112">
-        <f>2980+571</f>
-        <v>3551</v>
+        <f>2980+698</f>
+        <v>3678</v>
       </c>
       <c r="BC28" s="111">
         <v>4105</v>
@@ -13215,19 +13215,19 @@
       </c>
       <c r="E29" s="158">
         <f t="shared" si="83"/>
-        <v>0.78666016968585184</v>
+        <v>0.78301994955285481</v>
       </c>
       <c r="F29" s="86">
         <f t="shared" si="24"/>
-        <v>27445</v>
+        <v>27318</v>
       </c>
       <c r="G29" s="158">
         <f t="shared" si="84"/>
-        <v>0.21333983031414813</v>
+        <v>0.21698005044714516</v>
       </c>
       <c r="H29" s="145">
         <f t="shared" si="26"/>
-        <v>7443</v>
+        <v>7570</v>
       </c>
       <c r="I29" s="159">
         <f t="shared" si="85"/>
@@ -13369,11 +13369,11 @@
       </c>
       <c r="AW29" s="109">
         <f t="shared" si="97"/>
-        <v>0.511243951038998</v>
+        <v>0.49316823228010248</v>
       </c>
       <c r="AX29" s="109">
         <f t="shared" si="98"/>
-        <v>0.488756048961002</v>
+        <v>0.50683176771989757</v>
       </c>
       <c r="AY29" s="110">
         <f t="shared" si="54"/>
@@ -13384,11 +13384,11 @@
       </c>
       <c r="BA29" s="119">
         <f t="shared" si="45"/>
-        <v>3592</v>
+        <v>3465</v>
       </c>
       <c r="BB29" s="112">
-        <f>2863+571</f>
-        <v>3434</v>
+        <f>2863+698</f>
+        <v>3561</v>
       </c>
       <c r="BC29" s="111">
         <v>2173</v>
@@ -13456,19 +13456,19 @@
       </c>
       <c r="E30" s="158">
         <f t="shared" si="83"/>
-        <v>0.73850147741663141</v>
+        <v>0.73403405093569718</v>
       </c>
       <c r="F30" s="86">
         <f t="shared" si="24"/>
-        <v>20994.12</v>
+        <v>20867.12</v>
       </c>
       <c r="G30" s="158">
         <f t="shared" si="84"/>
-        <v>0.26149852258336853</v>
+        <v>0.26596594906430282</v>
       </c>
       <c r="H30" s="145">
         <f t="shared" si="26"/>
-        <v>7433.88</v>
+        <v>7560.88</v>
       </c>
       <c r="I30" s="159">
         <f t="shared" si="85"/>
@@ -13610,11 +13610,11 @@
       </c>
       <c r="AW30" s="109">
         <f t="shared" si="97"/>
-        <v>0.40356509884117242</v>
+        <v>0.38192229038854802</v>
       </c>
       <c r="AX30" s="109">
         <f t="shared" si="98"/>
-        <v>0.59643490115882758</v>
+        <v>0.61807770961145192</v>
       </c>
       <c r="AY30" s="110">
         <f t="shared" si="54"/>
@@ -13625,11 +13625,11 @@
       </c>
       <c r="BA30" s="119">
         <f t="shared" si="45"/>
-        <v>2368.12</v>
+        <v>2241.12</v>
       </c>
       <c r="BB30" s="112">
-        <f>2928.88+571</f>
-        <v>3499.88</v>
+        <f>2928.88+698</f>
+        <v>3626.88</v>
       </c>
       <c r="BC30" s="111">
         <v>2212.1999999999998</v>
@@ -13697,19 +13697,19 @@
       </c>
       <c r="E31" s="158">
         <f t="shared" si="83"/>
-        <v>0.86814317059791557</v>
+        <v>0.86596612726275368</v>
       </c>
       <c r="F31" s="86">
         <f t="shared" si="24"/>
-        <v>50644</v>
+        <v>50517</v>
       </c>
       <c r="G31" s="158">
         <f t="shared" si="84"/>
-        <v>0.13185682940208449</v>
+        <v>0.13403387273724629</v>
       </c>
       <c r="H31" s="145">
         <f t="shared" si="26"/>
-        <v>7692</v>
+        <v>7819</v>
       </c>
       <c r="I31" s="159">
         <f t="shared" si="85"/>
@@ -13851,11 +13851,11 @@
       </c>
       <c r="AW31" s="109">
         <f t="shared" si="97"/>
-        <v>0.62972889392846099</v>
+        <v>0.61663746005566433</v>
       </c>
       <c r="AX31" s="109">
         <f t="shared" si="98"/>
-        <v>0.37027110607153901</v>
+        <v>0.38336253994433561</v>
       </c>
       <c r="AY31" s="110">
         <f t="shared" si="54"/>
@@ -13866,11 +13866,11 @@
       </c>
       <c r="BA31" s="119">
         <f t="shared" si="45"/>
-        <v>6109</v>
+        <v>5982</v>
       </c>
       <c r="BB31" s="112">
-        <f>3021+571</f>
-        <v>3592</v>
+        <f>3021+698</f>
+        <v>3719</v>
       </c>
       <c r="BC31" s="111">
         <v>3879</v>
@@ -13938,19 +13938,19 @@
       </c>
       <c r="E32" s="158">
         <f t="shared" si="83"/>
-        <v>0.87060915962650065</v>
+        <v>0.86843725416424389</v>
       </c>
       <c r="F32" s="86">
         <f t="shared" si="24"/>
-        <v>50908</v>
+        <v>50781</v>
       </c>
       <c r="G32" s="158">
         <f t="shared" si="84"/>
-        <v>0.12939084037349932</v>
+        <v>0.13156274583575606</v>
       </c>
       <c r="H32" s="145">
         <f t="shared" si="26"/>
-        <v>7566</v>
+        <v>7693</v>
       </c>
       <c r="I32" s="159">
         <f t="shared" si="85"/>
@@ -14092,11 +14092,11 @@
       </c>
       <c r="AW32" s="168">
         <f t="shared" si="97"/>
-        <v>0.63419401296162947</v>
+        <v>0.62112951342454481</v>
       </c>
       <c r="AX32" s="168">
         <f t="shared" si="98"/>
-        <v>0.36580598703837053</v>
+        <v>0.37887048657545519</v>
       </c>
       <c r="AY32" s="110">
         <f t="shared" si="54"/>
@@ -14107,11 +14107,11 @@
       </c>
       <c r="BA32" s="119">
         <f t="shared" si="45"/>
-        <v>6165</v>
+        <v>6038</v>
       </c>
       <c r="BB32" s="112">
-        <f>2985+571</f>
-        <v>3556</v>
+        <f>2985+698</f>
+        <v>3683</v>
       </c>
       <c r="BC32" s="111">
         <v>4291</v>
@@ -14179,19 +14179,19 @@
       </c>
       <c r="E33" s="158">
         <f t="shared" si="83"/>
-        <v>0.87133905698262137</v>
+        <v>0.86914076022986919</v>
       </c>
       <c r="F33" s="86">
         <f t="shared" si="24"/>
-        <v>50339</v>
+        <v>50212</v>
       </c>
       <c r="G33" s="158">
         <f t="shared" si="84"/>
-        <v>0.12866094301737865</v>
+        <v>0.13085923977013086</v>
       </c>
       <c r="H33" s="145">
         <f t="shared" si="26"/>
-        <v>7433</v>
+        <v>7560</v>
       </c>
       <c r="I33" s="159">
         <f t="shared" si="85"/>
@@ -14332,11 +14332,11 @@
       </c>
       <c r="AW33" s="168">
         <f t="shared" si="97"/>
-        <v>0.6297947335683185</v>
+        <v>0.61662865436450343</v>
       </c>
       <c r="AX33" s="168">
         <f t="shared" si="98"/>
-        <v>0.3702052664316815</v>
+        <v>0.38337134563549657</v>
       </c>
       <c r="AY33" s="110">
         <f t="shared" si="54"/>
@@ -14347,11 +14347,11 @@
       </c>
       <c r="BA33" s="119">
         <f t="shared" si="45"/>
-        <v>6075</v>
+        <v>5948</v>
       </c>
       <c r="BB33" s="112">
-        <f>3000+571</f>
-        <v>3571</v>
+        <f>3000+698</f>
+        <v>3698</v>
       </c>
       <c r="BC33" s="111">
         <v>4751</v>
@@ -14419,19 +14419,19 @@
       </c>
       <c r="E34" s="158">
         <f t="shared" si="83"/>
-        <v>0.87331138415586174</v>
+        <v>0.87115606544022806</v>
       </c>
       <c r="F34" s="86">
         <f t="shared" si="24"/>
-        <v>51459</v>
+        <v>51332</v>
       </c>
       <c r="G34" s="158">
         <f t="shared" si="84"/>
-        <v>0.12668861584413821</v>
+        <v>0.12884393455977192</v>
       </c>
       <c r="H34" s="145">
         <f t="shared" si="26"/>
-        <v>7465</v>
+        <v>7592</v>
       </c>
       <c r="I34" s="159">
         <f t="shared" si="85"/>
@@ -14573,11 +14573,11 @@
       </c>
       <c r="AW34" s="109">
         <f t="shared" si="97"/>
-        <v>0.63277006638503319</v>
+        <v>0.619995976664655</v>
       </c>
       <c r="AX34" s="109">
         <f t="shared" si="98"/>
-        <v>0.36722993361496681</v>
+        <v>0.380004023335345</v>
       </c>
       <c r="AY34" s="110">
         <f t="shared" si="54"/>
@@ -14588,11 +14588,11 @@
       </c>
       <c r="BA34" s="119">
         <f t="shared" si="45"/>
-        <v>6291</v>
+        <v>6164</v>
       </c>
       <c r="BB34" s="112">
-        <f>3080+571</f>
-        <v>3651</v>
+        <f>3080+698</f>
+        <v>3778</v>
       </c>
       <c r="BC34" s="111">
         <v>4325</v>
@@ -14660,19 +14660,19 @@
       </c>
       <c r="E35" s="158">
         <f t="shared" ref="E35" si="103">F35/D35</f>
-        <v>0.87124204425893026</v>
+        <v>0.86905152043051559</v>
       </c>
       <c r="F35" s="86">
         <f t="shared" ref="F35" si="104">D35-H35</f>
-        <v>50512</v>
+        <v>50385</v>
       </c>
       <c r="G35" s="158">
         <f t="shared" ref="G35" si="105">H35/D35</f>
-        <v>0.12875795574106974</v>
+        <v>0.13094847956948444</v>
       </c>
       <c r="H35" s="145">
         <f t="shared" ref="H35" si="106">U35+AG35+AQ35+BB35</f>
-        <v>7465</v>
+        <v>7592</v>
       </c>
       <c r="I35" s="159">
         <f t="shared" ref="I35" si="107">AE35/(AE35+AO35+BL35+AY35)</f>
@@ -14814,11 +14814,11 @@
       </c>
       <c r="AW35" s="109">
         <f t="shared" ref="AW35" si="121">BA35/AZ35</f>
-        <v>0.63277006638503319</v>
+        <v>0.619995976664655</v>
       </c>
       <c r="AX35" s="109">
         <f t="shared" ref="AX35" si="122">BB35/AZ35</f>
-        <v>0.36722993361496681</v>
+        <v>0.380004023335345</v>
       </c>
       <c r="AY35" s="110">
         <f t="shared" ref="AY35" si="123">BA35+BB35</f>
@@ -14829,11 +14829,11 @@
       </c>
       <c r="BA35" s="119">
         <f t="shared" ref="BA35" si="124">AZ35-BB35</f>
-        <v>6291</v>
+        <v>6164</v>
       </c>
       <c r="BB35" s="112">
-        <f>3080+571</f>
-        <v>3651</v>
+        <f>3080+698</f>
+        <v>3778</v>
       </c>
       <c r="BC35" s="111">
         <v>4325</v>
@@ -14901,19 +14901,19 @@
       </c>
       <c r="E36" s="158">
         <f t="shared" si="83"/>
-        <v>0.78710162357185809</v>
+        <v>0.78328322309079979</v>
       </c>
       <c r="F36" s="86">
         <f t="shared" si="24"/>
-        <v>26179</v>
+        <v>26052</v>
       </c>
       <c r="G36" s="158">
         <f t="shared" si="84"/>
-        <v>0.21289837642814191</v>
+        <v>0.21671677690920024</v>
       </c>
       <c r="H36" s="145">
         <f t="shared" si="26"/>
-        <v>7081</v>
+        <v>7208</v>
       </c>
       <c r="I36" s="159">
         <f t="shared" si="85"/>
@@ -15055,11 +15055,11 @@
       </c>
       <c r="AW36" s="109">
         <f t="shared" si="97"/>
-        <v>0.30390607360578009</v>
+        <v>0.27523142921652743</v>
       </c>
       <c r="AX36" s="109">
         <f t="shared" si="98"/>
-        <v>0.69609392639421996</v>
+        <v>0.72476857078347257</v>
       </c>
       <c r="AY36" s="110">
         <f t="shared" si="54"/>
@@ -15070,11 +15070,11 @@
       </c>
       <c r="BA36" s="119">
         <f t="shared" si="45"/>
-        <v>1346</v>
+        <v>1219</v>
       </c>
       <c r="BB36" s="112">
-        <f>2512+571</f>
-        <v>3083</v>
+        <f>2512+698</f>
+        <v>3210</v>
       </c>
       <c r="BC36" s="111">
         <v>1858</v>
@@ -15140,19 +15140,19 @@
       </c>
       <c r="E37" s="158">
         <f t="shared" ref="E37" si="128">F37/D37</f>
-        <v>0.74070197474007393</v>
+        <v>0.73627102086386154</v>
       </c>
       <c r="F37" s="86">
         <f t="shared" si="24"/>
-        <v>21230</v>
+        <v>21103</v>
       </c>
       <c r="G37" s="158">
         <f t="shared" ref="G37" si="129">H37/D37</f>
-        <v>0.25929802525992601</v>
+        <v>0.26372897913613846</v>
       </c>
       <c r="H37" s="145">
         <f t="shared" si="26"/>
-        <v>7432</v>
+        <v>7559</v>
       </c>
       <c r="I37" s="159">
         <f t="shared" ref="I37" si="130">AE37/(AE37+AO37+BL37+AY37)</f>
@@ -15294,11 +15294,11 @@
       </c>
       <c r="AW37" s="109">
         <f t="shared" ref="AW37" si="139">BA37/AZ37</f>
-        <v>0.23331130204890946</v>
+        <v>0.20533157083057943</v>
       </c>
       <c r="AX37" s="109">
         <f t="shared" ref="AX37" si="140">BB37/AZ37</f>
-        <v>0.76668869795109051</v>
+        <v>0.7946684291694206</v>
       </c>
       <c r="AY37" s="110">
         <f t="shared" si="54"/>
@@ -15309,11 +15309,11 @@
       </c>
       <c r="BA37" s="119">
         <f t="shared" si="45"/>
-        <v>1059</v>
+        <v>932</v>
       </c>
       <c r="BB37" s="112">
-        <f>2909+571</f>
-        <v>3480</v>
+        <f>2909+698</f>
+        <v>3607</v>
       </c>
       <c r="BC37" s="111">
         <v>1492</v>
@@ -15412,6 +15412,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="BJ1:BR2"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="AN3:AN4"/>
+    <mergeCell ref="AR3:AU3"/>
+    <mergeCell ref="BJ3:BJ4"/>
+    <mergeCell ref="BK3:BK4"/>
+    <mergeCell ref="BL3:BN3"/>
+    <mergeCell ref="BO3:BR3"/>
+    <mergeCell ref="AW1:BH2"/>
+    <mergeCell ref="AW3:AW4"/>
+    <mergeCell ref="AX3:AX4"/>
+    <mergeCell ref="AY3:BB3"/>
+    <mergeCell ref="BC3:BH3"/>
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="D1:P2"/>
     <mergeCell ref="R1:AA2"/>
@@ -15428,22 +15444,6 @@
     <mergeCell ref="AE3:AG3"/>
     <mergeCell ref="AH3:AK3"/>
     <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="BJ1:BR2"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="AN3:AN4"/>
-    <mergeCell ref="AR3:AU3"/>
-    <mergeCell ref="BJ3:BJ4"/>
-    <mergeCell ref="BK3:BK4"/>
-    <mergeCell ref="BL3:BN3"/>
-    <mergeCell ref="BO3:BR3"/>
-    <mergeCell ref="AW1:BH2"/>
-    <mergeCell ref="AW3:AW4"/>
-    <mergeCell ref="AX3:AX4"/>
-    <mergeCell ref="AY3:BB3"/>
-    <mergeCell ref="BC3:BH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="88" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -19571,6 +19571,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -19817,29 +19839,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1CA4DF3-E0D3-49AF-B438-8BD78918604D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F6CD966-312F-4DCA-8C69-58CB492BFB83}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{125D77FA-E0FF-4A11-A689-C362ECE8E93F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19856,23 +19875,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F6CD966-312F-4DCA-8C69-58CB492BFB83}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1CA4DF3-E0D3-49AF-B438-8BD78918604D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
-    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>